--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/LOUISIANA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/LOUISIANA_2019.xlsx
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C167">
